--- a/Assets/Resources/ExcelData/CharacterInfoTable.xlsx
+++ b/Assets/Resources/ExcelData/CharacterInfoTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project_DungeonMayer\Assets\Resources\ExcelData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project_DT\Assets\Resources\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375C1A3A-475E-4C72-AA97-AE3C8B8CA5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62932A7B-332F-4147-96FA-B3C71A53F5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="3210" windowWidth="21600" windowHeight="11295" xr2:uid="{B7C1E6BB-5843-456B-8CF8-F8F9A197622A}"/>
+    <workbookView xWindow="3630" yWindow="1785" windowWidth="21600" windowHeight="11295" xr2:uid="{B7C1E6BB-5843-456B-8CF8-F8F9A197622A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -118,44 +118,36 @@
     <t>헌터 9</t>
   </si>
   <si>
-    <t>Dresscostume17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume47</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume51</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume68</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dresscostume122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Dresscostume01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dresscostume02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dresscostume03</t>
+  </si>
+  <si>
+    <t>Dresscostume04</t>
+  </si>
+  <si>
+    <t>Dresscostume05</t>
+  </si>
+  <si>
+    <t>Dresscostume06</t>
+  </si>
+  <si>
+    <t>Dresscostume07</t>
+  </si>
+  <si>
+    <t>Dresscostume08</t>
+  </si>
+  <si>
+    <t>Dresscostume09</t>
+  </si>
+  <si>
+    <t>Dresscostume10</t>
   </si>
 </sst>
 </file>
